--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486352_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486352_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8663</v>
+        <v>2.6543</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1325</v>
+        <v>1.7972</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7338</v>
+        <v>0.8571</v>
       </c>
       <c r="G2" t="n">
         <v>1.6726</v>
@@ -610,13 +610,13 @@
         <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3237</v>
+        <v>0.1118</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5396</v>
+        <v>0.2043</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2158</v>
+        <v>-0.0925</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2854</v>
+        <v>0.9367</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-0.2411</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0853</v>
+        <v>1.1777</v>
       </c>
       <c r="G3" t="n">
         <v>0.4515</v>
@@ -688,13 +688,13 @@
         <v>0.6525</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0139</v>
+        <v>-0.3626</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.822</v>
+        <v>-0.2632</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1919</v>
+        <v>-0.0994</v>
       </c>
       <c r="V3" t="n">
         <v>0.1952</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>T. BORG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1634</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1619</v>
+        <v>0.2645</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9985000000000001</v>
+        <v>-0.3308</v>
       </c>
       <c r="G4" t="n">
-        <v>0.315</v>
+        <v>-0.2529</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4564</v>
+        <v>0.52</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7713</v>
+        <v>-0.773</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0912</v>
+        <v>1.4342</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1095</v>
+        <v>1.7004</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0183</v>
+        <v>-0.2661</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2238</v>
+        <v>-1.6872</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5659</v>
+        <v>-1.1803</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7897</v>
+        <v>-0.5068</v>
       </c>
       <c r="P4" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R4" t="n">
-        <v>1.305</v>
+        <v>2.6101</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8033</v>
+        <v>-0.5873</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0707</v>
+        <v>0.2452</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2674</v>
+        <v>-0.8325</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.2599</v>
+        <v>0.339</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.2599</v>
+        <v>-0.4212</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. VRANKIC</t>
+          <t>A. WINTERING</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1474</v>
+        <v>-0.3216</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3929</v>
+        <v>0.1738</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5403</v>
+        <v>-0.4954</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.6863</v>
+        <v>-1.7417</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.8335</v>
+        <v>-1.2891</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.8528</v>
+        <v>-0.4526</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.1816</v>
+        <v>-0.751</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.9847</v>
+        <v>-0.6562</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.1969</v>
+        <v>-0.0948</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5047</v>
+        <v>-0.9907</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8488</v>
+        <v>-0.6328</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6558</v>
+        <v>-0.3578</v>
       </c>
       <c r="P5" t="n">
-        <v>2.6101</v>
+        <v>2.1751</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.6101</v>
+        <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7643</v>
+        <v>-0.1592</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4238</v>
+        <v>0.1646</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6595</v>
+        <v>-0.3239</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1645</v>
+        <v>-0.5958</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1507</v>
+        <v>0.7602</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.9862</v>
+        <v>-1.356</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. WINTERING</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5837</v>
+        <v>-0.4378</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2732</v>
+        <v>0.7149</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3105</v>
+        <v>-1.1526</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.7417</v>
+        <v>0.315</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2891</v>
+        <v>-0.4564</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4526</v>
+        <v>0.7713</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.751</v>
+        <v>0.0912</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6562</v>
+        <v>0.1095</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0948</v>
+        <v>-0.0183</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9907</v>
+        <v>0.2238</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6328</v>
+        <v>-0.5659</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3578</v>
+        <v>0.7897</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4213</v>
+        <v>0.2022</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2824</v>
+        <v>0.6237</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1389</v>
+        <v>-0.4215</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5958</v>
+        <v>-2.2599</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.356</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9031</v>
+        <v>-0.5563</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.083</v>
+        <v>-0.8595</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1799</v>
+        <v>0.3032</v>
       </c>
       <c r="G7" t="n">
         <v>-1.5849</v>
@@ -1000,13 +1000,13 @@
         <v>1.9576</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0752</v>
+        <v>0.2716</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.2151</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0668</v>
+        <v>0.0565</v>
       </c>
       <c r="V7" t="n">
         <v>-0.113</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-0.7341</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0502</v>
+        <v>-0.6032</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1465</v>
+        <v>-0.1309</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0553</v>
@@ -1078,13 +1078,13 @@
         <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.103</v>
+        <v>-0.9334</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3509</v>
+        <v>0.0961</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7522</v>
+        <v>-1.0296</v>
       </c>
       <c r="V8" t="n">
         <v>2.3422</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>J. VRANKIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6231</v>
+        <v>-1.6504</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0766</v>
+        <v>-1.1717</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5465</v>
+        <v>-0.4786</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2529</v>
+        <v>-4.6863</v>
       </c>
       <c r="H9" t="n">
-        <v>0.52</v>
+        <v>-1.8335</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.773</v>
+        <v>-2.8528</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4342</v>
+        <v>-3.1816</v>
       </c>
       <c r="K9" t="n">
-        <v>1.7004</v>
+        <v>-0.9847</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2661</v>
+        <v>-2.1969</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6872</v>
+        <v>-1.5047</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1803</v>
+        <v>-0.8488</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5068</v>
+        <v>-0.6558</v>
       </c>
       <c r="P9" t="n">
-        <v>0.435</v>
+        <v>2.6101</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>2.6101</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1442</v>
+        <v>0.2614</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0959</v>
+        <v>0.8592</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0482</v>
+        <v>-0.5979</v>
       </c>
       <c r="V9" t="n">
-        <v>0.339</v>
+        <v>0.1645</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7602</v>
+        <v>1.1507</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.4212</v>
+        <v>-0.9862</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8081</v>
+        <v>-4.0066</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6922</v>
+        <v>-3.9216</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1158</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3254</v>
@@ -1234,13 +1234,13 @@
         <v>0.435</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6526</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4817</v>
+        <v>0.2524</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.7982</v>
       </c>
       <c r="V10" t="n">
         <v>-0.4828</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.9536</v>
+        <v>-4.7012</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.7392</v>
+        <v>-4.7334</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2144</v>
+        <v>0.0322</v>
       </c>
       <c r="G11" t="n">
         <v>-3.83</v>
@@ -1312,13 +1312,13 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.1236</v>
+        <v>-0.8712</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0959</v>
+        <v>-0.0901</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0277</v>
+        <v>-0.7811</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.1595</v>
+        <v>-6.884</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2693</v>
+        <v>-4.7164</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8902</v>
+        <v>-2.1676</v>
       </c>
       <c r="G12" t="n">
         <v>-2.8079</v>
@@ -1390,13 +1390,13 @@
         <v>1.5225</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5227</v>
+        <v>0.7982</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2762</v>
+        <v>0.8292</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2465</v>
+        <v>-0.031</v>
       </c>
       <c r="V12" t="n">
         <v>-4.2218</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.7671</v>
+        <v>-15.7672</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.2963</v>
+        <v>-13.2965</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4707</v>
+        <v>-2.470700000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-15.8453</v>
@@ -1450,13 +1450,13 @@
         <v>-1.6136</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.9022</v>
+        <v>-5.902200000000001</v>
       </c>
       <c r="N13" t="n">
         <v>-5.826199999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.07580000000000009</v>
+        <v>-0.07580000000000031</v>
       </c>
       <c r="P13" t="n">
         <v>6.5252</v>
@@ -1468,13 +1468,13 @@
         <v>16.3129</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8146</v>
+        <v>-1.8144</v>
       </c>
       <c r="T13" t="n">
         <v>3.1365</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.951000000000001</v>
+        <v>-4.951099999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-4.632400000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.0464</v>
+        <v>10.8152</v>
       </c>
       <c r="E14" t="n">
-        <v>8.6898</v>
+        <v>8.242699999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3567</v>
+        <v>2.5725</v>
       </c>
       <c r="G14" t="n">
         <v>9.000400000000001</v>
@@ -1546,13 +1546,13 @@
         <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1662</v>
+        <v>-0.3975</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3447</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5109</v>
+        <v>-1.2951</v>
       </c>
       <c r="V14" t="n">
         <v>1.7772</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.6423</v>
+        <v>5.6943</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4633</v>
+        <v>4.7927</v>
       </c>
       <c r="F15" t="n">
-        <v>1.179</v>
+        <v>0.9016</v>
       </c>
       <c r="G15" t="n">
         <v>2.127</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4506</v>
+        <v>0.5026</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7557</v>
+        <v>1.0851</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3051</v>
+        <v>-0.5825</v>
       </c>
       <c r="V15" t="n">
         <v>2.6297</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.954</v>
+        <v>4.6072</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8698</v>
+        <v>3.6462</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0843</v>
+        <v>0.961</v>
       </c>
       <c r="G16" t="n">
         <v>3.1185</v>
@@ -1702,13 +1702,13 @@
         <v>0.435</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7962</v>
+        <v>0.4494</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8051</v>
+        <v>0.5816</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0089</v>
+        <v>-0.1322</v>
       </c>
       <c r="V16" t="n">
         <v>0.8218</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5439</v>
+        <v>1.3667</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0582</v>
+        <v>-1.8347</v>
       </c>
       <c r="F17" t="n">
-        <v>3.6021</v>
+        <v>3.2014</v>
       </c>
       <c r="G17" t="n">
         <v>1.4759</v>
@@ -1780,13 +1780,13 @@
         <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9418</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1971</v>
+        <v>0.4206</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7447</v>
+        <v>0.344</v>
       </c>
       <c r="V17" t="n">
         <v>0.4313</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7245</v>
+        <v>0.9518</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1428</v>
+        <v>-0.2546</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8673</v>
+        <v>1.2063</v>
       </c>
       <c r="G18" t="n">
         <v>1.5484</v>
@@ -1858,13 +1858,13 @@
         <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.781</v>
+        <v>-0.5537</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3341</v>
+        <v>0.2223</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1151</v>
+        <v>-0.776</v>
       </c>
       <c r="V18" t="n">
         <v>0.1745</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ZUBIZARRETA ARANBARRI</t>
+          <t>G. MAIZA APECECHEA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3116</v>
+        <v>0.2749</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8073</v>
+        <v>-0.1173</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4957</v>
+        <v>0.3922</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2568</v>
+        <v>0.4982</v>
       </c>
       <c r="H19" t="n">
-        <v>0.301</v>
+        <v>-0.2222</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5578</v>
+        <v>0.7204</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6703</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0365</v>
+        <v>-0.8149</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7068</v>
+        <v>0.8248</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4136</v>
+        <v>0.4883</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2645</v>
+        <v>0.5927</v>
       </c>
       <c r="O19" t="n">
-        <v>0.149</v>
+        <v>-0.1044</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0548</v>
+        <v>0.0595</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.137</v>
+        <v>0.3954</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0822</v>
+        <v>-0.3359</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. MAIZA APECECHEA</t>
+          <t>A. ZUBIZARRETA ARANBARRI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3686</v>
+        <v>-0.0765</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4526</v>
+        <v>-0.6955</v>
       </c>
       <c r="F20" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.619</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4982</v>
+        <v>-0.2568</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2222</v>
+        <v>0.301</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7204</v>
+        <v>-0.5578</v>
       </c>
       <c r="J20" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.6703</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8149</v>
+        <v>0.0365</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8248</v>
+        <v>-0.7068</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4883</v>
+        <v>0.4136</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5927</v>
+        <v>0.2645</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1044</v>
+        <v>0.149</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6525</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.584</v>
+        <v>0.1803</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0601</v>
+        <v>-0.0252</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6441</v>
+        <v>0.2055</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6552</v>
+        <v>-0.7361</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.943</v>
+        <v>-2.0547</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2878</v>
+        <v>1.3186</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2358</v>
@@ -2092,13 +2092,13 @@
         <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>1.084</v>
+        <v>1.0031</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0791</v>
+        <v>0.9674</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0049</v>
+        <v>0.0357</v>
       </c>
       <c r="V21" t="n">
         <v>0.0615</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. MOTOS CABODEVILLA</t>
+          <t>T. MCGHIE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4455</v>
+        <v>-3.3699</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1908</v>
+        <v>-5.1901</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7453</v>
+        <v>1.8202</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5806</v>
+        <v>-0.0111</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5686</v>
+        <v>2.232</v>
       </c>
       <c r="I22" t="n">
-        <v>0.012</v>
+        <v>-2.2431</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0257</v>
+        <v>-1.2596</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2404</v>
+        <v>1.6242</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2661</v>
+        <v>-2.8838</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6063</v>
+        <v>1.2485</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3282</v>
+        <v>0.6078</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2781</v>
+        <v>0.6407</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.0451</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q22" t="n">
         <v>-4.5676</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>0.714</v>
+        <v>-0.5927</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4026</v>
+        <v>0.0721</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3115</v>
+        <v>-0.6649</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.695</v>
+        <v>0.0615</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.695</v>
+        <v>-0.5034</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. MCGHIE</t>
+          <t>M. MOTOS CABODEVILLA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2948</v>
+        <v>-3.692</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.0842</v>
+        <v>-4.1908</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7894</v>
+        <v>0.4987</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0111</v>
+        <v>0.5806</v>
       </c>
       <c r="H23" t="n">
-        <v>2.232</v>
+        <v>0.5686</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.2431</v>
+        <v>0.012</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2596</v>
+        <v>-0.0257</v>
       </c>
       <c r="K23" t="n">
-        <v>1.6242</v>
+        <v>0.2404</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.8838</v>
+        <v>-0.2661</v>
       </c>
       <c r="M23" t="n">
-        <v>1.2485</v>
+        <v>0.6063</v>
       </c>
       <c r="N23" t="n">
-        <v>0.6078</v>
+        <v>0.3282</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6407</v>
+        <v>0.2781</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.8276</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q23" t="n">
         <v>-4.5676</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5176</v>
+        <v>0.4675</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.822</v>
+        <v>0.4026</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6957</v>
+        <v>0.0649</v>
       </c>
       <c r="V23" t="n">
-        <v>0.0615</v>
+        <v>-1.695</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5034</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>15.8354</v>
+        <v>15.8356</v>
       </c>
       <c r="E24" t="n">
-        <v>2.344</v>
+        <v>2.3439</v>
       </c>
       <c r="F24" t="n">
-        <v>13.4916</v>
+        <v>13.4915</v>
       </c>
       <c r="G24" t="n">
         <v>15.8453</v>
@@ -2299,13 +2299,13 @@
         <v>1.6894</v>
       </c>
       <c r="J24" t="n">
-        <v>5.902100000000001</v>
+        <v>5.9021</v>
       </c>
       <c r="K24" t="n">
         <v>5.8261</v>
       </c>
       <c r="L24" t="n">
-        <v>0.07590000000000074</v>
+        <v>0.07590000000000052</v>
       </c>
       <c r="M24" t="n">
         <v>9.943299999999999</v>
@@ -2323,16 +2323,16 @@
         <v>-16.3128</v>
       </c>
       <c r="R24" t="n">
-        <v>9.787699999999999</v>
+        <v>9.787700000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>1.883</v>
+        <v>1.8831</v>
       </c>
       <c r="T24" t="n">
-        <v>5.0195</v>
+        <v>5.0196</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.1365</v>
+        <v>-3.136499999999999</v>
       </c>
       <c r="V24" t="n">
         <v>4.6323</v>
